--- a/tests/fixtures/excel/sorts_sorted.xlsx
+++ b/tests/fixtures/excel/sorts_sorted.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FEB2C900-19A1-4301-8900-741256BCE731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{31846231-ADA8-4ACD-82E0-41442DD1BDA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="51420" windowHeight="21100" xr2:uid="{CC53D324-1B14-46D3-A0E3-D28456BA7752}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="51420" windowHeight="21100" xr2:uid="{262E2A39-EE50-4708-89AF-7AF7ED5DB406}"/>
   </bookViews>
   <sheets>
     <sheet name="Values" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,15 @@
     <sheet name="ArrayRow" sheetId="17" r:id="rId17"/>
     <sheet name="Spill" sheetId="18" r:id="rId18"/>
     <sheet name="Kinds" sheetId="19" r:id="rId19"/>
+    <sheet name="Table" sheetId="20" r:id="rId20"/>
+    <sheet name="TableKeys" sheetId="21" r:id="rId21"/>
+    <sheet name="TableFiltered" sheetId="22" r:id="rId22"/>
+    <sheet name="TableHeadless" sheetId="23" r:id="rId23"/>
+    <sheet name="TableRange" sheetId="24" r:id="rId24"/>
+    <sheet name="Filter" sheetId="25" r:id="rId25"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">Filter!$A$1:$C$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">Filtered!$A$1:$C$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -60,7 +67,30 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{CDD6A659-E77B-44A5-90E7-F642389EAAEE}">
+    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{46CA2372-732B-4D7B-83B1-9B5444E277A9}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>note on C3</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="C7" authorId="0" shapeId="0" xr:uid="{1713C157-7BED-4BBD-9456-11D901197607}">
       <text>
         <r>
           <rPr>
@@ -100,7 +130,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="107">
   <si>
     <t>i</t>
   </si>
@@ -282,6 +312,27 @@
     <t>FI</t>
   </si>
   <si>
+    <t>１</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>²</t>
+  </si>
+  <si>
+    <t>a​b</t>
+  </si>
+  <si>
+    <t>ς</t>
+  </si>
+  <si>
+    <t>Σ</t>
+  </si>
+  <si>
+    <t>σ</t>
+  </si>
+  <si>
     <t>k</t>
   </si>
   <si>
@@ -394,6 +445,12 @@
   </si>
   <si>
     <t>j</t>
+  </si>
+  <si>
+    <t>calc</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
@@ -515,6 +572,87 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FC82F03E-355E-4D9E-A749-1969D6620A65}" name="Sales" displayName="Sales" ref="A1:D8" totalsRowCount="1">
+  <autoFilter ref="A1:D7" xr:uid="{FC82F03E-355E-4D9E-A749-1969D6620A65}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D7">
+    <sortCondition descending="1" ref="B2:B7"/>
+  </sortState>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{81F57500-8760-4A27-86FE-BB07B42CEFE8}" name="i" totalsRowLabel="Total"/>
+    <tableColumn id="2" xr3:uid="{0BFCDA98-6E90-4612-AAC4-BF4848890D3F}" name="k" totalsRowFunction="sum"/>
+    <tableColumn id="3" xr3:uid="{7FA42CB2-23F8-4BD5-B4FF-864388D9259E}" name="c"/>
+    <tableColumn id="4" xr3:uid="{DAC19856-693E-4791-8622-4332B0847360}" name="calc" totalsRowFunction="sum">
+      <calculatedColumnFormula>Sales[[#This Row],[k]]*2</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EE8F1840-AF47-40A1-A91C-D5CBE2A076FF}" name="Grid" displayName="Grid" ref="C3:E8" totalsRowShown="0">
+  <autoFilter ref="C3:E8" xr:uid="{EE8F1840-AF47-40A1-A91C-D5CBE2A076FF}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" caseSensitive="1" ref="C4:E8">
+    <sortCondition ref="D4:D8"/>
+    <sortCondition descending="1" ref="E4:E8"/>
+  </sortState>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{D5D19F4E-722C-4349-B57E-4B2764CE409A}" name="i"/>
+    <tableColumn id="2" xr3:uid="{48EE4C43-2807-4DE2-9C87-A8E3FBAEC33A}" name="k"/>
+    <tableColumn id="3" xr3:uid="{9C919877-828E-4798-ADFB-4A1276FD2CEA}" name="c"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{AE50CAF6-0C55-4B91-B64F-2342ECCB3208}" name="Seen" displayName="Seen" ref="A1:C7" totalsRowShown="0">
+  <autoFilter ref="A1:C7" xr:uid="{AE50CAF6-0C55-4B91-B64F-2342ECCB3208}">
+    <filterColumn colId="1">
+      <customFilters>
+        <customFilter operator="greaterThan" val="25"/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C7">
+    <sortCondition descending="1" ref="B2:B7"/>
+  </sortState>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{27A84B9F-A5FE-4C3E-BF9A-B9A0FAAECE1E}" name="i"/>
+    <tableColumn id="2" xr3:uid="{5D8784A7-7764-4CD6-9379-37F7DD01AC88}" name="k"/>
+    <tableColumn id="3" xr3:uid="{873B0B38-EDA6-4B83-8A39-9E152BC2FBE4}" name="c"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{BAEA760B-A45F-40BC-AF84-836485C11D1D}" name="Bare" displayName="Bare" ref="A2:C7" headerRowCount="0" totalsRowShown="0">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C7">
+    <sortCondition ref="B2:B7"/>
+  </sortState>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{321A6FC0-BB4E-4165-B778-AA7D6D183440}" name="i"/>
+    <tableColumn id="2" xr3:uid="{FE29F7CA-A48A-4C18-AB87-57EF45686EBD}" name="k"/>
+    <tableColumn id="3" xr3:uid="{6E2CCEA2-3F80-433E-9DDF-9AE8591B7AE3}" name="c"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F9AC88BC-7063-493E-B432-0A414334C44D}" name="Whole" displayName="Whole" ref="A1:C8" totalsRowCount="1">
+  <autoFilter ref="A1:C7" xr:uid="{F9AC88BC-7063-493E-B432-0A414334C44D}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{E5B6B6CD-360A-4FB3-B1E5-457B58FCC497}" name="i" totalsRowLabel="Total"/>
+    <tableColumn id="2" xr3:uid="{0D290711-F4AC-4FBD-ABA1-660864B65C34}" name="k" totalsRowFunction="sum"/>
+    <tableColumn id="3" xr3:uid="{405B8BA1-3EFC-4138-BD58-F03752BD6CD8}" name="c" totalsRowFunction="count"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -833,7 +971,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{171E35EC-46AD-47A4-A029-A5D4F62D6CFF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{755858AC-5CBC-4C32-8242-D76A4CF992AA}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:B45"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1206,7 +1344,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{685B8750-8B6E-4AFD-812F-AF3C75193390}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F21C981-F066-43AF-BA24-04C36A13F96F}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -1215,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -1229,7 +1367,7 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
@@ -1240,7 +1378,7 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -1251,7 +1389,7 @@
         <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -1262,7 +1400,7 @@
         <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
@@ -1273,7 +1411,7 @@
         <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -1284,7 +1422,7 @@
         <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1296,7 +1434,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA8EA863-4431-4424-882C-C73534FBDEF9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6A1F8D7-335D-47A6-90F6-18279CE6E866}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1306,10 +1444,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -1320,7 +1458,7 @@
         <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
@@ -1331,7 +1469,7 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -1342,7 +1480,7 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
@@ -1353,7 +1491,7 @@
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -1364,7 +1502,7 @@
         <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -1375,11 +1513,11 @@
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C7" xr:uid="{CA8EA863-4431-4424-882C-C73534FBDEF9}">
+  <autoFilter ref="A1:C7" xr:uid="{C6A1F8D7-335D-47A6-90F6-18279CE6E866}">
     <filterColumn colId="1">
       <customFilters>
         <customFilter operator="greaterThan" val="25"/>
@@ -1394,7 +1532,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E46C7255-7CFE-4C7C-8609-1AECA801B028}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8273F2E7-A9B9-4649-8725-97143D7C65BC}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -1403,10 +1541,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -1417,7 +1555,7 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -1428,7 +1566,7 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -1439,7 +1577,7 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -1450,7 +1588,7 @@
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -1462,7 +1600,7 @@
         <v/>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -1470,7 +1608,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -1487,13 +1625,13 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F662BD9-8368-493E-B749-45D4F2D42519}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72DD65F4-84E3-4444-B571-736BF8D93F3B}">
   <dimension ref="B1:F8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.35">
@@ -1501,7 +1639,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.35">
@@ -1509,7 +1647,7 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.35">
@@ -1517,7 +1655,7 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.35">
@@ -1525,7 +1663,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.35">
@@ -1533,12 +1671,12 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.35">
       <c r="F8" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1550,7 +1688,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D821EF53-D81D-4253-9982-CF57931B3372}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86D97DD2-86E9-4B63-A588-765E8EA5085F}">
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -1559,7 +1697,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -1689,7 +1827,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC2950F3-4531-45CA-88AF-D2C1A5DC2002}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71177957-309F-4B9E-BC67-5D34C31B106B}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -1698,10 +1836,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -1712,7 +1850,7 @@
         <v>30</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D2" s="11"/>
     </row>
@@ -1724,7 +1862,7 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -1735,7 +1873,7 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -1746,7 +1884,7 @@
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -1757,7 +1895,7 @@
         <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -1768,7 +1906,7 @@
         <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1783,7 +1921,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{983A0A1C-F6AC-48DA-ABF9-389BFE76DB97}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1187A9D5-7F51-43F4-9052-F699C3CA1417}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -1792,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -1806,7 +1944,7 @@
         <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -1817,7 +1955,7 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D3">
         <f t="array" ref="D3:D4">B3:B4*2</f>
@@ -1832,7 +1970,7 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D4">
         <v>100</v>
@@ -1846,7 +1984,7 @@
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -1857,7 +1995,7 @@
         <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -1868,7 +2006,7 @@
         <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1880,7 +2018,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51BABC0F-AC4F-44D2-A615-F9E0B9CF5EA9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7941E5C-7639-475C-8C32-E2D882202C42}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -1889,10 +2027,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -1903,7 +2041,7 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -1914,7 +2052,7 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -1925,7 +2063,7 @@
         <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -1936,7 +2074,7 @@
         <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -1962,7 +2100,7 @@
         <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1974,7 +2112,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84B95DBD-29C0-40B9-A92C-3D24B7C38BC8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D3A681B-7E80-44EC-A1B0-20FE49C13497}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -1983,10 +2121,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -1997,7 +2135,7 @@
         <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D2" cm="1">
         <f t="array" ref="D2:D4">_xlfn.SEQUENCE(3)</f>
@@ -2012,7 +2150,7 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -2026,7 +2164,7 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -2040,7 +2178,7 @@
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -2051,7 +2189,7 @@
         <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -2062,7 +2200,7 @@
         <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -2074,7 +2212,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BB7AE77-5E5B-4380-BA10-0254E64B9A8C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD89AEBC-573E-43D5-94EE-21CEBE4D649A}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -2083,10 +2221,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -2097,7 +2235,7 @@
         <v>#N/A</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -2108,7 +2246,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -2119,7 +2257,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -2130,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -2138,10 +2276,10 @@
         <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -2152,7 +2290,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -2175,7 +2313,7 @@
         <v>36161</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -2186,7 +2324,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -2220,7 +2358,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9142A331-7CE8-46F7-A3FB-F89F5F92C679}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FA7E503-9625-420F-B5D9-5F5F0375C9F8}">
   <dimension ref="A1:B45"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -2591,9 +2729,596 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C8DF8E-E536-49BA-96B1-CB115646D1BA}">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>60</v>
+      </c>
+      <c r="C2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D2">
+        <f>Sales[[#This Row],[k]]*2</f>
+        <v>120</v>
+      </c>
+      <c r="F2">
+        <f>B3</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>50</v>
+      </c>
+      <c r="C3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3">
+        <f>Sales[[#This Row],[k]]*2</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4">
+        <f>Sales[[#This Row],[k]]*2</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5">
+        <f>Sales[[#This Row],[k]]*2</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6">
+        <f>Sales[[#This Row],[k]]*2</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7">
+        <f>Sales[[#This Row],[k]]*2</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>106</v>
+      </c>
+      <c r="B8">
+        <f>SUBTOTAL(109,Sales[k])</f>
+        <v>210</v>
+      </c>
+      <c r="D8">
+        <f>SUBTOTAL(109,Sales[calc])</f>
+        <v>420</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC0C9FEE-5707-4E64-8FC9-C248113A31BC}">
+  <dimension ref="C3:E8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="3" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F48ED99B-A66B-4891-A60A-D01E9D27454D}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>60</v>
+      </c>
+      <c r="C2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>50</v>
+      </c>
+      <c r="C4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E7B1948-7891-46AB-B2E2-9C5AD8145912}">
+  <dimension ref="A2:C7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <v>50</v>
+      </c>
+      <c r="C6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>60</v>
+      </c>
+      <c r="C7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CE424E6-6A6B-44B7-A925-BBB4BA656ABE}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B2">
+        <f ca="1">SUBTOTAL(109,Whole[k])</f>
+        <v>210</v>
+      </c>
+      <c r="C2">
+        <f ca="1">SUBTOTAL(103,Whole[c])</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>60</v>
+      </c>
+      <c r="C3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>50</v>
+      </c>
+      <c r="C4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C8">
+    <sortCondition descending="1" ref="B2:B8"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87B9BD2D-90F4-4CAD-ABCE-323BA0F29C24}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>60</v>
+      </c>
+      <c r="C2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>50</v>
+      </c>
+      <c r="C4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C7" xr:uid="{87B9BD2D-90F4-4CAD-ABCE-323BA0F29C24}">
+    <filterColumn colId="1">
+      <customFilters>
+        <customFilter operator="greaterThan" val="15"/>
+      </customFilters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C7">
+      <sortCondition descending="1" ref="B2:B7"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E6C48BE-B196-4A79-8EBA-B3CC974735CC}">
-  <dimension ref="A1:B44"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F9BB788-30D7-4411-B926-8F04ED338B00}">
+  <dimension ref="A1:B52"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -2606,359 +3331,423 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>6</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>9</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37">
+        <v>8</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38">
+        <v>11</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44">
+        <v>30</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>31</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>33</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>34</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>35</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49">
         <v>36</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B49" s="3" t="s">
         <v>53</v>
       </c>
     </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>50</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>48</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>49</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" caseSensitive="1" ref="A2:B44">
-    <sortCondition ref="B2:B44"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" caseSensitive="1" ref="A2:B52">
+    <sortCondition ref="B2:B52"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9C809DE-2F65-4801-93EE-B7BF87E11DBB}">
-  <dimension ref="A1:B44"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CD2CCD9-FF33-4851-AAC2-381CC4DF5796}">
+  <dimension ref="A1:B52"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -2971,359 +3760,423 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44">
+        <v>27</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>26</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>25</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>24</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48">
         <v>23</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B48" s="3" t="s">
         <v>6</v>
       </c>
     </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>45</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>46</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>43</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>44</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" caseSensitive="1" ref="A2:B44">
-    <sortCondition descending="1" ref="B2:B44"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" caseSensitive="1" ref="A2:B52">
+    <sortCondition descending="1" ref="B2:B52"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A6DFF26-4F02-47AC-A77F-D26F36D6E8AE}">
-  <dimension ref="A1:B44"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC2D007E-C03D-40B8-BFD7-974D6C5199F0}">
+  <dimension ref="A1:B52"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -3336,358 +4189,422 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>6</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>9</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37">
+        <v>8</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44">
+        <v>31</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>32</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>33</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>34</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>35</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49">
         <v>36</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B49" s="3" t="s">
         <v>53</v>
       </c>
     </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B44">
-    <sortCondition ref="B2:B44"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B52">
+    <sortCondition ref="B2:B52"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54BDE4FA-BAA9-40FE-84FA-F696149DF637}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5321EA36-EAEF-4853-B6FE-3A34351430C9}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -3696,10 +4613,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C1" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -3707,7 +4624,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -3718,7 +4635,7 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -3729,7 +4646,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -3740,7 +4657,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -3751,7 +4668,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -3762,7 +4679,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -3773,7 +4690,7 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -3784,7 +4701,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -3795,7 +4712,7 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -3811,7 +4728,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AD2B58E-3E73-479F-9682-CD29E79C5A9F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FFAFF1E-BF6F-47EB-B248-221353049EE0}">
   <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -3820,22 +4737,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C1" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="D1" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E1" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F1" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G1" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.35">
@@ -3861,7 +4778,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3891,7 +4808,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H3" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -3913,7 +4830,7 @@
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.35">
@@ -3939,7 +4856,7 @@
         <v>183</v>
       </c>
       <c r="H5" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -3965,7 +4882,7 @@
         <v>320</v>
       </c>
       <c r="H6" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
@@ -3990,13 +4907,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5" xr:uid="{C3355BDB-C5E0-462C-BF9E-0291E85896F6}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5" xr:uid="{C463DCAE-261B-4DD0-AB32-57874070CB35}">
       <formula1>1</formula1>
       <formula2>9</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A6" r:id="rId1" display="https://example.com/a4" xr:uid="{21E3E891-169E-4925-865C-11E44100AF41}"/>
+    <hyperlink ref="A6" r:id="rId1" display="https://example.com/a4" xr:uid="{F3302B46-3CE5-4A33-81C8-F81AF63939C3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId2"/>
@@ -4004,7 +4921,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E124294C-D222-427F-8DDB-C1E798F38DCC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2746B21-89FD-4608-9FBE-904F91CF6162}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -4013,10 +4930,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -4027,7 +4944,7 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D2" t="str">
         <f t="shared" ref="D2:D7" si="0">A2&amp;C2</f>
@@ -4042,7 +4959,7 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D3" t="str">
         <f t="shared" si="0"/>
@@ -4057,7 +4974,7 @@
         <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D4" t="str">
         <f t="shared" si="0"/>
@@ -4072,7 +4989,7 @@
         <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D5" t="str">
         <f t="shared" si="0"/>
@@ -4087,7 +5004,7 @@
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D6" t="str">
         <f t="shared" si="0"/>
@@ -4102,7 +5019,7 @@
         <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="D7" t="str">
         <f t="shared" si="0"/>
@@ -4118,7 +5035,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E721D530-638F-4221-8232-48C77D271B0E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF682835-1A32-4724-A6E1-A19AEA444E69}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -4130,7 +5047,7 @@
         <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -4141,7 +5058,7 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -4152,7 +5069,7 @@
         <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -4163,7 +5080,7 @@
         <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -4174,7 +5091,7 @@
         <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -4185,7 +5102,7 @@
         <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
